--- a/AMS/007-Farry/Farry_CHS-Draft-Financials-2025-26-V2.xlsx
+++ b/AMS/007-Farry/Farry_CHS-Draft-Financials-2025-26-V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\007-Farry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BCBD96-6767-48B5-9C47-279A990A91F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4FF3E0-AAC2-40E6-BCA2-BDC297ECEA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="719" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Workings" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BS!$A$1:$H$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BS!$A$1:$M$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'FA-Sh'!$A$1:$I$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'FD-Sch'!$A$1:$L$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">IE!$A$1:$H$58</definedName>
@@ -850,10 +850,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="&quot;Mumbai: &quot;dd&quot;th&quot;\ mmmm\,\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="&quot;Mumbai: &quot;dd&quot;th&quot;\ mmmm\,\ yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -1368,47 +1368,47 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1417,49 +1417,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1469,58 +1469,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1539,35 +1539,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="21" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1579,34 +1579,34 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="25" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1615,20 +1615,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1643,13 +1643,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1661,10 +1661,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1679,13 +1679,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1697,19 +1697,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1721,7 +1721,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1742,8 +1742,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1775,103 +1859,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2177,61 +2177,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="156" t="s">
         <v>254</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="154"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="158"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="159" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="157"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="161"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="157"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="161"/>
     </row>
     <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="162" t="s">
         <v>253</v>
       </c>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="160"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="164"/>
     </row>
     <row r="5" spans="1:10" s="44" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="83">
         <v>45747</v>
       </c>
-      <c r="B5" s="161" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="162"/>
+      <c r="B5" s="165" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="166"/>
       <c r="D5" s="87">
         <v>46112</v>
       </c>
@@ -2239,10 +2239,10 @@
         <f>+A5</f>
         <v>45747</v>
       </c>
-      <c r="F5" s="161" t="s">
+      <c r="F5" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="162"/>
+      <c r="G5" s="166"/>
       <c r="H5" s="84">
         <f>+D5</f>
         <v>46112</v>
@@ -3062,10 +3062,10 @@
         <f>SUM(A9:A48)</f>
         <v>24402395.289999999</v>
       </c>
-      <c r="B49" s="169" t="s">
+      <c r="B49" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="169"/>
+      <c r="C49" s="155"/>
       <c r="D49" s="92">
         <f>SUM(D10:D48)</f>
         <v>25128188.670000002</v>
@@ -3074,10 +3074,10 @@
         <f>SUM(E6:E48)</f>
         <v>24402395.289999999</v>
       </c>
-      <c r="F49" s="169" t="s">
+      <c r="F49" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="169"/>
+      <c r="G49" s="155"/>
       <c r="H49" s="82">
         <f>SUM(H6:H48)</f>
         <v>25128188.670000002</v>
@@ -3100,13 +3100,13 @@
       <c r="B51" s="132"/>
       <c r="C51" s="132"/>
       <c r="D51" s="77"/>
-      <c r="E51" s="163" t="str">
+      <c r="E51" s="149" t="str">
         <f>"For "&amp;A1</f>
         <v>For FARRY APARTMENT CO-OPERATIVE HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="F51" s="163"/>
-      <c r="G51" s="163"/>
-      <c r="H51" s="164"/>
+      <c r="F51" s="149"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="150"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="133"/>
@@ -3151,10 +3151,10 @@
       <c r="B55" s="136"/>
       <c r="C55" s="137"/>
       <c r="D55" s="77"/>
-      <c r="E55" s="165"/>
-      <c r="F55" s="165"/>
-      <c r="G55" s="165"/>
-      <c r="H55" s="166"/>
+      <c r="E55" s="151"/>
+      <c r="F55" s="151"/>
+      <c r="G55" s="151"/>
+      <c r="H55" s="152"/>
       <c r="J55" s="50"/>
       <c r="L55" s="50"/>
       <c r="P55" s="50"/>
@@ -3166,12 +3166,12 @@
       <c r="B56" s="136"/>
       <c r="C56" s="137"/>
       <c r="D56" s="77"/>
-      <c r="E56" s="165" t="s">
+      <c r="E56" s="151" t="s">
         <v>257</v>
       </c>
-      <c r="F56" s="165"/>
-      <c r="G56" s="165"/>
-      <c r="H56" s="166"/>
+      <c r="F56" s="151"/>
+      <c r="G56" s="151"/>
+      <c r="H56" s="152"/>
       <c r="J56" s="50"/>
       <c r="N56" s="50"/>
       <c r="O56" s="50"/>
@@ -3194,11 +3194,11 @@
       <c r="Q57" s="50"/>
     </row>
     <row r="58" spans="1:17" s="50" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="167">
+      <c r="A58" s="153">
         <v>46228</v>
       </c>
-      <c r="B58" s="168"/>
-      <c r="C58" s="168"/>
+      <c r="B58" s="154"/>
+      <c r="C58" s="154"/>
       <c r="D58" s="78"/>
       <c r="E58" s="79"/>
       <c r="F58" s="79"/>
@@ -3215,18 +3215,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="E51:H51"/>
     <mergeCell ref="E55:H55"/>
     <mergeCell ref="E56:H56"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3254,63 +3254,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="152" t="str">
+      <c r="A1" s="156" t="str">
         <f>BS!A1</f>
         <v>FARRY APARTMENT CO-OPERATIVE HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="154"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="158"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="159" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="157"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="161"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="155" t="s">
+      <c r="A3" s="159" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156"/>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="157"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="161"/>
     </row>
     <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="162" t="s">
         <v>252</v>
       </c>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="160"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="163"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="164"/>
     </row>
     <row r="5" spans="1:8" s="44" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="84">
         <f>+BS!E5</f>
         <v>45747</v>
       </c>
-      <c r="B5" s="170" t="s">
+      <c r="B5" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="170"/>
+      <c r="C5" s="169"/>
       <c r="D5" s="139">
         <f>BS!D5</f>
         <v>46112</v>
@@ -3319,10 +3319,10 @@
         <f>+A5</f>
         <v>45747</v>
       </c>
-      <c r="F5" s="170" t="s">
+      <c r="F5" s="169" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="170"/>
+      <c r="G5" s="169"/>
       <c r="H5" s="84">
         <f>+D5</f>
         <v>46112</v>
@@ -4153,10 +4153,10 @@
         <f>SUM(A6:A48)</f>
         <v>1467953</v>
       </c>
-      <c r="B49" s="171" t="s">
+      <c r="B49" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="172"/>
+      <c r="C49" s="168"/>
       <c r="D49" s="92">
         <f>SUM(D6:D48)</f>
         <v>1675308</v>
@@ -4165,10 +4165,10 @@
         <f>SUM(E6:E48)</f>
         <v>1467953</v>
       </c>
-      <c r="F49" s="171" t="s">
+      <c r="F49" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="G49" s="172"/>
+      <c r="G49" s="168"/>
       <c r="H49" s="82">
         <f>SUM(H7:H48)</f>
         <v>1675308</v>
@@ -4195,13 +4195,13 @@
       <c r="B51" s="132"/>
       <c r="C51" s="132"/>
       <c r="D51" s="77"/>
-      <c r="E51" s="163" t="str">
+      <c r="E51" s="149" t="str">
         <f>"For "&amp;A1</f>
         <v>For FARRY APARTMENT CO-OPERATIVE HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="F51" s="163"/>
-      <c r="G51" s="163"/>
-      <c r="H51" s="164"/>
+      <c r="F51" s="149"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="150"/>
     </row>
     <row r="52" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="133"/>
@@ -4242,10 +4242,10 @@
       <c r="B55" s="136"/>
       <c r="C55" s="137"/>
       <c r="D55" s="77"/>
-      <c r="E55" s="165"/>
-      <c r="F55" s="165"/>
-      <c r="G55" s="165"/>
-      <c r="H55" s="166"/>
+      <c r="E55" s="151"/>
+      <c r="F55" s="151"/>
+      <c r="G55" s="151"/>
+      <c r="H55" s="152"/>
       <c r="J55" s="50"/>
       <c r="L55" s="50"/>
       <c r="P55" s="50"/>
@@ -4257,12 +4257,12 @@
       <c r="B56" s="136"/>
       <c r="C56" s="137"/>
       <c r="D56" s="77"/>
-      <c r="E56" s="165" t="s">
+      <c r="E56" s="151" t="s">
         <v>257</v>
       </c>
-      <c r="F56" s="165"/>
-      <c r="G56" s="165"/>
-      <c r="H56" s="166"/>
+      <c r="F56" s="151"/>
+      <c r="G56" s="151"/>
+      <c r="H56" s="152"/>
       <c r="J56" s="50"/>
       <c r="N56" s="50"/>
       <c r="O56" s="50"/>
@@ -4285,11 +4285,11 @@
       <c r="Q57" s="50"/>
     </row>
     <row r="58" spans="1:17" s="50" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="167">
+      <c r="A58" s="153">
         <v>46228</v>
       </c>
-      <c r="B58" s="168"/>
-      <c r="C58" s="168"/>
+      <c r="B58" s="154"/>
+      <c r="C58" s="154"/>
       <c r="D58" s="78"/>
       <c r="E58" s="79"/>
       <c r="F58" s="79"/>
@@ -4306,18 +4306,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="E51:H51"/>
     <mergeCell ref="E55:H55"/>
     <mergeCell ref="E56:H56"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4343,36 +4343,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="174" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="148"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
+      <c r="L1" s="176"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="177" t="s">
         <v>251</v>
       </c>
-      <c r="B2" s="150"/>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="150"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="151"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+      <c r="L2" s="179"/>
     </row>
     <row r="3" spans="1:18" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="93" t="s">
@@ -4511,11 +4511,11 @@
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="170" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="142"/>
-      <c r="C7" s="143"/>
+      <c r="B7" s="170"/>
+      <c r="C7" s="171"/>
       <c r="D7" s="98">
         <f>SUM(D5:D6)</f>
         <v>383420</v>
@@ -4792,11 +4792,11 @@
       <c r="L15" s="27"/>
     </row>
     <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="142" t="s">
+      <c r="A16" s="170" t="s">
         <v>259</v>
       </c>
-      <c r="B16" s="142"/>
-      <c r="C16" s="143"/>
+      <c r="B16" s="170"/>
+      <c r="C16" s="171"/>
       <c r="D16" s="101">
         <f>SUM(D9:D15)</f>
         <v>1699682</v>
@@ -4872,11 +4872,11 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="142" t="s">
+      <c r="A19" s="170" t="s">
         <v>259</v>
       </c>
-      <c r="B19" s="142"/>
-      <c r="C19" s="143"/>
+      <c r="B19" s="170"/>
+      <c r="C19" s="171"/>
       <c r="D19" s="101">
         <f>SUM(D18)</f>
         <v>15500</v>
@@ -5258,11 +5258,11 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="142" t="s">
+      <c r="A31" s="170" t="s">
         <v>259</v>
       </c>
-      <c r="B31" s="142"/>
-      <c r="C31" s="143"/>
+      <c r="B31" s="170"/>
+      <c r="C31" s="171"/>
       <c r="D31" s="101">
         <f>SUM(D21:D30)</f>
         <v>3903898</v>
@@ -5299,11 +5299,11 @@
       <c r="H32" s="21"/>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="145"/>
-      <c r="C33" s="145"/>
+      <c r="B33" s="173"/>
+      <c r="C33" s="173"/>
       <c r="D33" s="102">
         <f>D7+D16+D19+D31</f>
         <v>6002500</v>
@@ -5361,29 +5361,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="180" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="114" t="s">
@@ -5725,21 +5725,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="175" t="str">
+      <c r="A1" s="142" t="str">
         <f>+BS!A1</f>
         <v>FARRY APARTMENT CO-OPERATIVE HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="177"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="144"/>
     </row>
     <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="180" t="s">
+      <c r="A2" s="147" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="181"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="148"/>
       <c r="E2" s="123"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5799,11 +5799,11 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="179"/>
-      <c r="C7" s="179"/>
+      <c r="B7" s="146"/>
+      <c r="C7" s="146"/>
       <c r="D7" s="128">
         <f>SUM(D4:D6)</f>
         <v>35637</v>
@@ -5823,12 +5823,12 @@
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="178" t="s">
+      <c r="A11" s="145" t="s">
         <v>242</v>
       </c>
-      <c r="B11" s="178"/>
-      <c r="C11" s="178"/>
-      <c r="D11" s="178"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="125" t="s">
@@ -5929,11 +5929,11 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="179" t="s">
+      <c r="A19" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="179"/>
-      <c r="C19" s="179"/>
+      <c r="B19" s="146"/>
+      <c r="C19" s="146"/>
       <c r="D19" s="128">
         <f>SUM(D13:D18)</f>
         <v>25525</v>
@@ -5942,11 +5942,11 @@
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="178" t="s">
+      <c r="B22" s="145" t="s">
         <v>245</v>
       </c>
-      <c r="C22" s="178"/>
-      <c r="D22" s="178"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="145"/>
     </row>
     <row r="23" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="125" t="s">
@@ -6037,10 +6037,10 @@
       </c>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="179" t="s">
+      <c r="B31" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="179"/>
+      <c r="C31" s="146"/>
       <c r="D31" s="128">
         <f>SUM(D24:D30)</f>
         <v>73966</v>
@@ -6053,11 +6053,11 @@
     </row>
     <row r="33" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="178" t="s">
+      <c r="B34" s="145" t="s">
         <v>246</v>
       </c>
-      <c r="C34" s="178"/>
-      <c r="D34" s="178"/>
+      <c r="C34" s="145"/>
+      <c r="D34" s="145"/>
     </row>
     <row r="35" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="124" t="s">
@@ -6104,10 +6104,10 @@
       </c>
     </row>
     <row r="39" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="179" t="s">
+      <c r="B39" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="C39" s="179"/>
+      <c r="C39" s="146"/>
       <c r="D39" s="128">
         <f>SUM(D36:D38)</f>
         <v>32600</v>
